--- a/config/update_log44.xlsx
+++ b/config/update_log44.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -491,16 +491,16 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>7.031142602530156e-13</v>
+        <v>9.25343817704044e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>1.103699551035083e-12</v>
+        <v>1.297475161040134e-12</v>
       </c>
       <c r="F2" t="n">
         <v>1.246673502888672e-12</v>
       </c>
       <c r="G2" t="n">
-        <v>8.276526715781663e-13</v>
+        <v>1.159382807962353e-12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9.702849964387343e-13</v>
+        <v>1.157218822398801e-12</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -525,16 +525,16 @@
         <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>1.340387071850925</v>
+        <v>1.340387071851146</v>
       </c>
       <c r="E3" t="n">
-        <v>1.410982918495252</v>
+        <v>1.410982918495472</v>
       </c>
       <c r="F3" t="n">
-        <v>1.318381362768298</v>
+        <v>1.318381362768071</v>
       </c>
       <c r="G3" t="n">
-        <v>1.567578201172748</v>
+        <v>1.567578201172972</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.409332388571805</v>
+        <v>1.409332388571915</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -559,16 +559,16 @@
         <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>1.409476773943795</v>
+        <v>1.409476773943756</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9449033693983635</v>
+        <v>0.9449033693983343</v>
       </c>
       <c r="F4" t="n">
-        <v>14.84363755905597</v>
+        <v>14.84363755905601</v>
       </c>
       <c r="G4" t="n">
-        <v>2.534365165810236</v>
+        <v>2.534365165810216</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.93309571705209</v>
+        <v>4.933095717052079</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -630,13 +630,13 @@
         <v>6.047896892749694</v>
       </c>
       <c r="E6" t="n">
-        <v>2.394493265611804</v>
+        <v>2.394493265611571</v>
       </c>
       <c r="F6" t="n">
         <v>6.568571664130701</v>
       </c>
       <c r="G6" t="n">
-        <v>16.08860001579426</v>
+        <v>16.08860001579451</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7.774890459571615</v>
+        <v>7.77489045957162</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -661,16 +661,16 @@
         <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>2.375004867377296</v>
+        <v>2.375004867377916</v>
       </c>
       <c r="E7" t="n">
-        <v>1.177023867124076</v>
+        <v>1.177023867124088</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2444070606488734</v>
+        <v>0.2444070606488341</v>
       </c>
       <c r="G7" t="n">
-        <v>5.598088384030566</v>
+        <v>5.598088384030997</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.348631044795203</v>
+        <v>2.348631044795459</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -695,16 +695,16 @@
         <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7855009582655846</v>
+        <v>0.7855009582650173</v>
       </c>
       <c r="E8" t="n">
-        <v>1.276151425529617</v>
+        <v>1.276151425529799</v>
       </c>
       <c r="F8" t="n">
-        <v>6.913048364807105</v>
+        <v>6.91304836480653</v>
       </c>
       <c r="G8" t="n">
-        <v>3.724507495952592</v>
+        <v>3.724507495951821</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.174802061138725</v>
+        <v>3.174802061138291</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -729,16 +729,16 @@
         <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>57.53418897863642</v>
+        <v>57.53418897863686</v>
       </c>
       <c r="E9" t="n">
-        <v>3.557630387757944</v>
+        <v>3.557630387758373</v>
       </c>
       <c r="F9" t="n">
-        <v>2.325453671256079</v>
+        <v>2.325453671256921</v>
       </c>
       <c r="G9" t="n">
-        <v>2.369994745766823</v>
+        <v>2.369994745767274</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>16.44681694585432</v>
+        <v>16.44681694585486</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -831,16 +831,16 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3611891689692587</v>
+        <v>0.3611891689690888</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5187933234326534</v>
+        <v>0.5187933234325988</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3714344756613957</v>
+        <v>0.3714344756615828</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4853823437568477</v>
+        <v>0.4853823437567257</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4341998279550389</v>
+        <v>0.434199827954999</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -899,16 +899,16 @@
         <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>1.147783489840219</v>
+        <v>1.147783489840268</v>
       </c>
       <c r="E14" t="n">
-        <v>1.497173800626981</v>
+        <v>1.497173800627094</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5062487727419277</v>
+        <v>0.5062487727419204</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5483096468959274</v>
+        <v>0.5483096468958154</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9248789275262639</v>
+        <v>0.9248789275262745</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -967,13 +967,13 @@
         <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>2.384286892874059</v>
+        <v>2.384286892874168</v>
       </c>
       <c r="E16" t="n">
-        <v>3.025367628454206</v>
+        <v>3.025367628454442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7981016634130745</v>
+        <v>0.7981016634132366</v>
       </c>
       <c r="G16" t="n">
         <v>1.578147579185013</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.946475940981588</v>
+        <v>1.946475940981715</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
@@ -1035,13 +1035,13 @@
         <v>91</v>
       </c>
       <c r="D18" t="n">
-        <v>0.485546608574105</v>
+        <v>0.4855466085738275</v>
       </c>
       <c r="E18" t="n">
-        <v>5.383301008743277</v>
+        <v>5.383301008742823</v>
       </c>
       <c r="F18" t="n">
-        <v>7.520784476519684</v>
+        <v>7.520784476518803</v>
       </c>
       <c r="G18" t="n">
         <v>-1</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.463210697945688</v>
+        <v>4.463210697945151</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -1137,10 +1137,10 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>2.984704008659941</v>
+        <v>2.984704008660165</v>
       </c>
       <c r="E21" t="n">
-        <v>10.93890223354314</v>
+        <v>10.93890223354321</v>
       </c>
       <c r="F21" t="n">
         <v>6.971178206344957</v>
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.577369603920598</v>
+        <v>7.577369603920671</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -1208,13 +1208,13 @@
         <v>8.972482856313736</v>
       </c>
       <c r="E23" t="n">
-        <v>8.400980400727297</v>
+        <v>8.400980400727493</v>
       </c>
       <c r="F23" t="n">
-        <v>3.588678756121968</v>
+        <v>3.588678756121371</v>
       </c>
       <c r="G23" t="n">
-        <v>15.21781780532979</v>
+        <v>15.21781780533059</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>9.044989954623198</v>
+        <v>9.044989954623297</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -1273,16 +1273,16 @@
         <v>93</v>
       </c>
       <c r="D25" t="n">
-        <v>2.142692160443679</v>
+        <v>2.142692160443657</v>
       </c>
       <c r="E25" t="n">
-        <v>5.099490006364319</v>
+        <v>5.099490006364429</v>
       </c>
       <c r="F25" t="n">
-        <v>3.041654090036519</v>
+        <v>3.041654090036455</v>
       </c>
       <c r="G25" t="n">
-        <v>2.401802227785627</v>
+        <v>2.401802227785608</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1331,6 +1331,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>